--- a/AAII_Financials/Yearly/NTTYY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/NTTYY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="92">
   <si>
     <t>NTTYY</t>
   </si>
@@ -656,219 +656,231 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="17" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="18" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44651</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44286</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43921</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43555</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43190</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42825</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42460</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42094</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41729</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41364</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40999</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>90620600</v>
+      </c>
+      <c r="E8" s="3">
         <v>91518600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>88424000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>98817400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>100107400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>107993400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>110587300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>107209100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>110937800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>76775400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>84826300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>94643100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>100074600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>97269700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>94986600</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>79889900</v>
+      </c>
+      <c r="E9" s="3">
         <v>80503000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>75710900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>85058800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>85543200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>75377800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>78389500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>74987000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>77465500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>37260900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>41351400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>45073300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>44794200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>41543000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>39567500</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>10730600</v>
+      </c>
+      <c r="E10" s="3">
         <v>11015600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>12713000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>13758600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>14564200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>32615600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>32197800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>32222100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>33472300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>39514600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>43474900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>49569700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>55280400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>55726800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>55419000</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -887,37 +899,38 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>1752500</v>
+      </c>
+      <c r="E12" s="3">
         <v>1794100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1685100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1901800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>2042200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>2103200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>2090000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1907100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1963800</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>8</v>
@@ -928,15 +941,18 @@
       <c r="O12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P12" s="3">
+      <c r="P12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="3">
         <v>2447000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>2421400</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -982,105 +998,114 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-26900</v>
+      </c>
+      <c r="E14" s="3">
         <v>-8700</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-638500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-99500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-163100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>1648100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1560900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>2690500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1996800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>497800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>240500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>360000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>109200</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>334100</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>135800</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>11263700</v>
+      </c>
+      <c r="E15" s="3">
         <v>11499600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>10767200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>11905300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>12856200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>13627200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>13617900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>12035400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>12682400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>9855500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>12982500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>15592800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>17223500</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>34528300</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>17272700</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1096,104 +1121,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>79889900</v>
+      </c>
+      <c r="E17" s="3">
         <v>80503000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>75710900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>85058800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>85543200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>91230500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>94319900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>89228800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>92359400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>66397300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>74917400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>85391700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>88957500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>86343800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>83930900</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>10730600</v>
+      </c>
+      <c r="E18" s="3">
         <v>11015600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>12713000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>13758600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>14564200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>16762900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>16267400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>17980300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>18578400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>10378200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>9908900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>9251300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>11117100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>10925900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>11055600</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1212,248 +1244,264 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-288100</v>
+      </c>
+      <c r="E20" s="3">
         <v>-127500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-188500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-102900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-228700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-19300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-43400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>114900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>15500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>173500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>167400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>222500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1174600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>454700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>657100</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>22282400</v>
+      </c>
+      <c r="E21" s="3">
         <v>22642700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>23668700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>25766800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>27649200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>30409400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>29928600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>29900900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>31245300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>20451000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>22935200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>25249400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>29590300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>28682700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>29054100</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1425400</v>
+      </c>
+      <c r="E22" s="3">
         <v>995100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>721700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>525500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>410500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>381500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>305800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>229500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>325900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>254500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>306300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>375500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>436800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>493900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>509200</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>9948900</v>
+      </c>
+      <c r="E23" s="3">
         <v>10448900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>13093500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>13673500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>14786000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>14942000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>14592100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>15087600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>16387900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>10297200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>9770100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>9098300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>11854800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>10886600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>11203500</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>3140100</v>
+      </c>
+      <c r="E24" s="3">
         <v>3220500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>4200400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>3948700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>4443000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>4744300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>4263800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>4811600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>5025900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>3156800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>2608000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>3389400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>4456800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>4308200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>5313600</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1499,105 +1547,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>6808800</v>
+      </c>
+      <c r="E26" s="3">
         <v>7228400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>8893100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>9724800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>10343000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>10197700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>10328300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>10276000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>11362000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>7140300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>7162100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>5709000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>7398100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>6578400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>5889900</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>6522000</v>
+      </c>
+      <c r="E27" s="3">
         <v>6678000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>8459400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>9125700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>9726100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>8283800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>7948800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>7711900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>8454300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>5392900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>5422400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>4419100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>5362900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>4744400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>4228000</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1643,9 +1700,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1673,8 +1733,8 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>8</v>
+      <c r="L29" s="3">
+        <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>8</v>
@@ -1688,12 +1748,15 @@
       <c r="P29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
-      </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1739,9 +1802,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1787,105 +1853,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>288100</v>
+      </c>
+      <c r="E32" s="3">
         <v>127500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>188500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>102900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>228700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>19300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>43400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-114900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-15500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-173500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-167400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-222500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1174600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-454700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-657100</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>6522000</v>
+      </c>
+      <c r="E33" s="3">
         <v>6678000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>8459400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>9125700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>9726100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>8283800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>7948800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>7711900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>8454300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>5392900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>5422400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>4419100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>5362900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>4744400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>4228000</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1931,110 +2006,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>6522000</v>
+      </c>
+      <c r="E35" s="3">
         <v>6678000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>8459400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>9125700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>9726100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>8283800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>7948800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>7711900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>8454300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>5392900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>5422400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>4419100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>5362900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>4744400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>4228000</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44651</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44286</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43921</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43555</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43190</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42825</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42460</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42094</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41729</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41364</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40999</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2053,8 +2137,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2073,56 +2158,60 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>12086900</v>
+      </c>
+      <c r="E41" s="3">
         <v>6684500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>6498100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>5972300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>6872600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>8460500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>9605500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>8538300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>8427100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>6235900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>7998800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>7243500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>9017700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>17478900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>9222100</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2139,374 +2228,398 @@
         <v>0</v>
       </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>265500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>230400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>417800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>465400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>430300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>243100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>310000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>356800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>488600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>2774600</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>34912000</v>
+      </c>
+      <c r="E43" s="3">
         <v>32593200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>31846600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>31492100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>29686600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>33498700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>34546800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>42147600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>39960800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>21273000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>23233900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>25827400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>25715200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>24910200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>22752800</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>3929600</v>
+      </c>
+      <c r="E44" s="3">
         <v>3716800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>3465400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>3892200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>3362800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2852100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2391500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2992800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>3334900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2462700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>3047200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>3331200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>3804200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>3188100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>2977500</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>20419600</v>
+      </c>
+      <c r="E45" s="3">
         <v>12901800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>13223300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>8704800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>7153700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3082500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>15524800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>5284100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3074400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>5403900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>5365300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>5573100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>5633000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>5117600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>4868800</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>71348100</v>
+      </c>
+      <c r="E46" s="3">
         <v>55896300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>55033500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>50061400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>47075700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>48159300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>62299000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>59380600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>55262600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>35805700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>39888300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>42285200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>44526900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>42443800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>42595900</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>111097800</v>
+      </c>
+      <c r="E47" s="3">
         <v>34644500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>33184900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>29126000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>32848200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>13657500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>7189700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>7885200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>15141900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>6604400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>7276200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>9023300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>8513300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>8263800</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>7580300</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>77343000</v>
+      </c>
+      <c r="E48" s="3">
         <v>77706000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>74952200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>78502400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>82526300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>89710700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>88607000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>81336900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>82973200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>65506200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>70206600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>83606500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>90131500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>88870100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>88649500</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>31148000</v>
+      </c>
+      <c r="E49" s="3">
         <v>28063100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>27831000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>25624200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>26062200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>25516000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>24859200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>22690100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>22887200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>20072000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>20827500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>24290600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>25627300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>36924700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>21512800</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2552,9 +2665,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2600,9 +2716,12 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2618,39 +2737,42 @@
       <c r="G52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H52" s="3">
+      <c r="H52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I52" s="3">
         <v>15478400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>14401100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>12377200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>12343900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>15238800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>16415500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>17386100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>17011100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>15914900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>14944400</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2696,57 +2818,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>293835200</v>
+      </c>
+      <c r="E54" s="3">
         <v>200753800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>195723900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>190386600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>196503800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>207646500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>213882000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>201201600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>202828900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>143227000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>154614000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>176592000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>185810000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>177701000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>175283000</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2765,8 +2893,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2785,296 +2914,315 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>19326600</v>
+      </c>
+      <c r="E57" s="3">
         <v>19028900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>19443500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>21117900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>20590100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>8442500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>8624600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>8231600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>8106000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>10871600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>11560100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>13473700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>14108700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>13059100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>13402600</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>29216900</v>
+      </c>
+      <c r="E58" s="3">
         <v>20395900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>18290100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>15387000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>15121800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>30402900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>20525900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>12738800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>10060300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>6224700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>4565400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>6152700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>6519400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>13638900</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>6863000</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>87759000</v>
+      </c>
+      <c r="E59" s="3">
         <v>15783700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>16675800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>10659600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>11285000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>22220600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>26503400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>20633300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>20047800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>10749300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>11371800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>12119500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>13051600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>11504500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>11322400</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>140454000</v>
+      </c>
+      <c r="E60" s="3">
         <v>59171800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>58475200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>51431000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>51480500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>67144900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>61407900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>47180500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>43523700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>27845600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>27497300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>31746000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>33679700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>31809400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>31588000</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>77191900</v>
+      </c>
+      <c r="E61" s="3">
         <v>54204200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>52544000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>53448200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>52482800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>45294800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>23643800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>26148000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>29605100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>21527900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>26267700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>31759000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>32239800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>29732300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>32062500</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>6000800</v>
+      </c>
+      <c r="E62" s="3">
         <v>3629100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>3571700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>3841200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>4289700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>4644400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>4238000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3841000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2584800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>15948900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>17903100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>18590700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>19582100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>20514200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>20800800</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3120,9 +3268,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3168,9 +3319,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3216,57 +3370,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>229576000</v>
+      </c>
+      <c r="E66" s="3">
         <v>124995600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>123706100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>120046200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>122240100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>133477200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>107354000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>94669800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>93929600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>82213500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>89685600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>102535000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>107846000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>102877000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>104024000</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3285,8 +3445,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3332,9 +3493,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3380,9 +3544,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3428,9 +3595,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3476,57 +3646,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>56137800</v>
+      </c>
+      <c r="E72" s="3">
         <v>64951600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>60018400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>61309500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>60064900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>63906600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>60407300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>53734400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>57680500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>37920300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>37295600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>43730400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>44044600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>47515900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>44194300</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3572,9 +3748,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3620,9 +3799,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3668,57 +3850,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>61178100</v>
+      </c>
+      <c r="E76" s="3">
         <v>68258600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>65083200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>64403000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>68205400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>68379500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>84209400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>83610800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>85215900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>61013700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>64928500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>74056300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>77964000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>74823800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>71258600</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3764,110 +3952,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44651</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44286</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43921</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43555</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43190</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42825</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42460</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42094</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41729</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41364</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40999</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>6522000</v>
+      </c>
+      <c r="E81" s="3">
         <v>6678000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>8459400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>9125700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>9726100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>8283800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>7948800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>7711900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>8454300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>5392900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>5422400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>4419100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>5362900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>4744400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>4228000</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3886,56 +4083,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>11263700</v>
+      </c>
+      <c r="E83" s="3">
         <v>11499600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>10767200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>11905300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>12856200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>9794200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>9710300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>8289100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>8804300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>9855500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>12982500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>15592800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>17223500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>17264100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>17322200</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3981,9 +4182,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4029,9 +4233,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4077,9 +4284,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4125,9 +4335,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4173,57 +4386,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>9340500</v>
+      </c>
+      <c r="E89" s="3">
         <v>15786700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>15696400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>17008500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>24789200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>27207000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>27836000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>21714300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>23928000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>19645200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>19947000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>20402200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>24987600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>22304000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>22675000</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4242,56 +4461,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-14186500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-14239200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-13778100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-13930800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-14477400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-16231300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-17252000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-15092000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-16459800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-8773400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-9302300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-12325100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-13617700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-13981500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-12611600</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4337,9 +4560,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4385,57 +4611,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-6436400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-13353400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-13151500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-13066000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-13992400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-12880200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-17218300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-16010600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-16441600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-14082000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-12934400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-15939000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-19298300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-16146100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-17820100</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4454,56 +4686,60 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>2729200</v>
+      </c>
+      <c r="E96" s="3">
         <v>2916700</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>2759800</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>3155900</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>3269000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>3241200</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>3297600</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>2830100</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>2555500</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-1671500</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-1471300</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-1704000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-1705400</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-1667200</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-1518500</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4549,9 +4785,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4597,9 +4836,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4645,151 +4887,163 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>2775600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2290700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1550100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-4439800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-11842900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-15276300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-9677000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-5272700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-9117100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-6615400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-5200700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-5783400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-5701600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-6773700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-8570400</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>111900</v>
+      </c>
+      <c r="E101" s="3">
         <v>-21600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>254400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>191500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>213000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>64800</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-128100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>30500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-71300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-46900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-54500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>166200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>223200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>82200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-36300</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>5791600</v>
+      </c>
+      <c r="E102" s="3">
         <v>121000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1249200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-305700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-833100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-884700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>812600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>461400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1702100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1099000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1757400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1154000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>211000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-533700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-3751700</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
